--- a/猫眼/data.xlsx
+++ b/猫眼/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,32 +453,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>好东西</t>
+          <t>新·驯龙高手</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>922.11万</t>
+          <t>446.74万</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80556</v>
+        <v>118802</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>孤星计划</t>
+          <t>酱园弄·悬案</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>478.94万</t>
+          <t>202.11万</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -487,558 +487,558 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59298</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>破·地狱</t>
+          <t>碟中谍8：最终清算</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>330.40万</t>
+          <t>174.42万</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9101</v>
+        <v>54888</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>误判</t>
+          <t>时间之子</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>265.15万</t>
+          <t>104.81万</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9555</v>
+        <v>47987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>因果报应</t>
+          <t>哆啦A梦：大雄的绘画奇遇记</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>187.94万</t>
+          <t>60.40万</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25372</v>
+        <v>25242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>好运来</t>
+          <t>疾速追杀：芭蕾杀姬</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.39万</t>
+          <t>55.08万</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23876</v>
+        <v>19933</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>毒液：最后一舞</t>
+          <t>潜艇总动员：冒险岛</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>77.57万</t>
+          <t>48.12万</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4675</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>雄狮少年2</t>
+          <t>星际宝贝史迪奇</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>77.45万</t>
+          <t>46.63万</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11941</v>
+        <v>17456</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>大突围</t>
+          <t>分手清单</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>62.13万</t>
+          <t>42.84万</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>823</v>
+        <v>55398</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>小倩</t>
+          <t>哪吒之魔童闹海</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60.84万</t>
+          <t>22.37万</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17036</v>
+        <v>7719</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>胜券在握</t>
+          <t>星月童话</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>53.35万</t>
+          <t>16.47万</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10837</v>
+        <v>10425</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>魔法坏女巫</t>
+          <t>私家侦探</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>53.23万</t>
+          <t>9.81万</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9191</v>
+        <v>13594</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>海洋奇缘2</t>
+          <t>水饺皇后</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>53.09万</t>
+          <t>5.86万</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15211</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>鸳鸯楼·惊魂</t>
+          <t>红嫁衣</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>42.02万</t>
+          <t>5.62万</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11604</v>
+        <v>8563</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>风流一代</t>
+          <t>永不失联的爱</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36.31万</t>
+          <t>4.20万</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2269</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>蜡笔小新：我们的恐龙日记</t>
+          <t>情书</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35.09万</t>
+          <t>4.01万</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11484</v>
+        <v>866</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>堡垒</t>
+          <t>幽灵公主</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23.35万</t>
+          <t>3.46万</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>913</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>志愿军：存亡之战</t>
+          <t>我的世界大电影</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21.65万</t>
+          <t>2.46万</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>889</v>
+        <v>974</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>哈利·波特与死亡圣器（下）</t>
+          <t>攻壳机动队</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16.18万</t>
+          <t>2.05万</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>角斗士2</t>
+          <t>你的名字。</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14.58万</t>
+          <t>1.89万</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2238</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>爆裂鼓手</t>
+          <t>海底小纵队：海啸大危机</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14.54万</t>
+          <t>1.78万</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4394</v>
+        <v>825</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>如父如子</t>
+          <t>猎金·游戏</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14.46万</t>
+          <t>1.43万</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5073</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>皇后乐队蒙特利尔现场演唱会</t>
+          <t>恋曲尘封</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12.35万</t>
+          <t>1.16万</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1453</v>
+        <v>4763</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>不想和你有遗憾</t>
+          <t>雪豹</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11.90万</t>
+          <t>1.10万</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4084</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>今年二十二</t>
+          <t>功夫梦：融合之道</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6.49万</t>
+          <t>0.99万</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5803</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>陌路无期</t>
+          <t>风起前的蒲公英</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.08万</t>
+          <t>0.81万</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>焚城</t>
+          <t>人生开门红</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4.57万</t>
+          <t>0.75万</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>923</v>
+        <v>719</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>出不去的房间</t>
+          <t>新龙门客栈（舞台纪录电影·越剧）</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.62万</t>
+          <t>0.74万</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2006</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>盛极一时的爱情</t>
+          <t>熊出没·重启未来</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3.47万</t>
+          <t>0.59万</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>&lt;0.1%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3490</v>
+        <v>422</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>哈利·波特与死亡圣器（上)</t>
+          <t>那山那人那狗</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.97万</t>
+          <t>0.47万</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1047,18 +1047,18 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>656</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>完美的日子</t>
+          <t>三个火枪手：米莱迪</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.28万</t>
+          <t>0.44万</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1067,18 +1067,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>美人鱼的夏天</t>
+          <t>孤独摇滚(下)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.68万</t>
+          <t>0.42万</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1087,18 +1087,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>508</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>百川东到海</t>
+          <t>夏季成人礼</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.10万</t>
+          <t>0.39万</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1107,18 +1107,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>海上钢琴师</t>
+          <t>天空之城</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.09万</t>
+          <t>0.30万</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1127,18 +1127,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>283</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>哈利·波特与混血王子</t>
+          <t>高兴神探</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.03万</t>
+          <t>0.29万</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,18 +1147,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>206</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>天地辽阔</t>
+          <t>新龙门客栈</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.87万</t>
+          <t>0.29万</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1167,18 +1167,18 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>113</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>噬魂岛</t>
+          <t>黎明的一切</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.68万</t>
+          <t>0.27万</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1187,18 +1187,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>531</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>蓦然回首</t>
+          <t>蓝白红三部曲之蓝</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.67万</t>
+          <t>0.26万</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1207,18 +1207,18 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>282</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>哈利·波特与凤凰社</t>
+          <t>红猪</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.66万</t>
+          <t>0.25万</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1227,18 +1227,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>路边野餐</t>
+          <t>一生交给党</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.60万</t>
+          <t>0.25万</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1247,18 +1247,18 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>我谈的那场恋爱</t>
+          <t>和我说早安</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0.54万</t>
+          <t>0.25万</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1267,18 +1267,18 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>伟大征程</t>
+          <t>大风杀</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0.46万</t>
+          <t>0.25万</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1287,18 +1287,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>哈利·波特与阿兹卡班的囚徒</t>
+          <t>哈尔的移动城堡</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.43万</t>
+          <t>0.25万</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1307,18 +1307,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>只此青绿</t>
+          <t>袁隆平</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.42万</t>
+          <t>0.24万</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1327,18 +1327,18 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>111</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>这个杀手不太冷</t>
+          <t>雷霆特攻队*</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.41万</t>
+          <t>0.23万</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1347,18 +1347,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>追幸福的人</t>
+          <t>我，何爷爷</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.39万</t>
+          <t>0.20万</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1367,18 +1367,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>哈利·波特与火焰杯</t>
+          <t>孤独摇滚（上）</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.38万</t>
+          <t>0.19万</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1387,18 +1387,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>江海儿女</t>
+          <t>寻秘自然：时间的形状</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.37万</t>
+          <t>0.17万</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1407,18 +1407,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>姥姥的外孙</t>
+          <t>黑炮事件</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0.35万</t>
+          <t>0.16万</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1427,18 +1427,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>热血燃烧</t>
+          <t>开心超人之逆世营救</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0.34万</t>
+          <t>0.15万</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1447,18 +1447,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>629</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>苍山</t>
+          <t>猫猫的奇幻漂流</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0.30万</t>
+          <t>0.15万</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1467,18 +1467,18 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>云上的云</t>
+          <t>但愿人长久</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0.29万</t>
+          <t>0.14万</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1487,18 +1487,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>父亲在远方</t>
+          <t>苍茫的天涯是我的爱</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0.25万</t>
+          <t>0.14万</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1507,18 +1507,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>出走的决心</t>
+          <t>还有明天</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0.24万</t>
+          <t>0.13万</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1527,18 +1527,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>哈利·波特与密室</t>
+          <t>我仍在此</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0.23万</t>
+          <t>0.11万</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1547,18 +1547,18 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>小孩不笨3</t>
+          <t>独一无二</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0.21万</t>
+          <t>0.10万</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1567,18 +1567,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>海绵宝宝：拯救比奇堡</t>
+          <t>十二公民</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0.20万</t>
+          <t>0.09万</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1587,18 +1587,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>213</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>火影忍者剧场版：忍者之路</t>
+          <t>新大头儿子和小头爸爸5：我的外星朋友</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0.20万</t>
+          <t>0.09万</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1607,18 +1607,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>熊猫计划</t>
+          <t>会计刺客2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.20万</t>
+          <t>0.07万</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1627,18 +1627,18 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>184</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>里斯本丸沉没</t>
+          <t>新大头儿子和小头爸爸4完美爸爸</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0.17万</t>
+          <t>0.06万</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1647,18 +1647,18 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>29</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>古宅谜案</t>
+          <t>同学们好</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0.15万</t>
+          <t>0.06万</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1667,18 +1667,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>凤鸣飞天</t>
+          <t>地上的云朵</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0.15万</t>
+          <t>0.05万</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1687,18 +1687,18 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>金钱堡垒</t>
+          <t>早春二月</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0.14万</t>
+          <t>0.05万</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1707,18 +1707,18 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>214</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>绝地飞行</t>
+          <t>致命玩偶</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0.14万</t>
+          <t>0.05万</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1727,18 +1727,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>青年邓颖超</t>
+          <t>新大头儿子和小头爸爸3：俄罗斯奇遇记</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0.14万</t>
+          <t>0.05万</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1747,18 +1747,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>小丑2：双重妄想</t>
+          <t>孤独的美食家 剧场版</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0.14万</t>
+          <t>0.04万</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1767,18 +1767,18 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>刮大风</t>
+          <t>冲·撞</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0.14万</t>
+          <t>0.04万</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1787,18 +1787,18 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>康熙与路易十四</t>
+          <t>雄狮少年</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0.13万</t>
+          <t>0.02万</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>再团圆</t>
+          <t>寻找嘎贝勒</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0.13万</t>
+          <t>0.02万</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1827,18 +1827,18 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>内沙</t>
+          <t>射雕英雄传：侠之大者</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0.12万</t>
+          <t>0.02万</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1847,18 +1847,18 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>乔妍的心事</t>
+          <t>有病才会喜欢你</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0.12万</t>
+          <t>0.02万</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1867,18 +1867,18 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>椰林深处</t>
+          <t>乐一通大电影：地球爆炸之日</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0.11万</t>
+          <t>0.01万</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1887,18 +1887,18 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>181</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>女人世界</t>
+          <t>日暮·归乡</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0.11万</t>
+          <t>0.01万</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1907,18 +1907,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>爱你很久很久</t>
+          <t>康熙与路易十四</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0.10万</t>
+          <t>0.01万</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1927,18 +1927,18 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>那个不为人知的故事</t>
+          <t>荒野机器人</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0.10万</t>
+          <t>0.01万</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1947,18 +1947,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>哈利·波特与魔法石</t>
+          <t>风起秋浦河</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0.10万</t>
+          <t>0.01万</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1967,18 +1967,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>红色一号：冬日行动</t>
+          <t>楝树花开</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0.09万</t>
+          <t>0.01万</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1987,18 +1987,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>追鱼</t>
+          <t>风味快餐车</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0.09万</t>
+          <t>0.00万</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2007,18 +2007,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>671</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>戴假发的人</t>
+          <t>红鬃烈马（京剧）</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0.08万</t>
+          <t>0.00万</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2027,18 +2027,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>我要当老师</t>
+          <t>海洋奇缘2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0.07万</t>
+          <t>0.00万</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2047,18 +2047,18 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>北极荒原</t>
+          <t>回农村干大事</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0.07万</t>
+          <t>0.00万</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2067,18 +2067,18 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>菊次郎的夏天</t>
+          <t>寻秘自然：地球往事</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0.05万</t>
+          <t>0.00万</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2093,12 +2093,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>最后的里程</t>
+          <t>戈壁行者</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0.04万</t>
+          <t>0.00万</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2107,326 +2107,6 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>阿莫阿依</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>0.04万</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>昆岗的号角</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>0.04万</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>749局</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>0.02万</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>向阳花开</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>0.01万</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>如果·爱</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>0.01万</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>江南：在爱开始的地方等你</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>0.01万</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>阁楼</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>0.01万</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>最后的告别</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>变形金刚：起源</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>“上海少女”的三十年</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>老枪</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>你是我的冠军</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>荒野机器人</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>生死搏斗</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>奇妙萌可大电影</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>悬崖之上</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>0.00万</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>&lt;0.1%</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
         <v>1</v>
       </c>
     </row>
